--- a/assets/report_templates/SPES_Report_Blank.xlsx
+++ b/assets/report_templates/SPES_Report_Blank.xlsx
@@ -70,22 +70,22 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -135,7 +135,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6600000" cy="750000"/>
+    <xdr:ext cx="11430000" cy="1298864"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="PESO Vinzons letterhead"/>
@@ -356,34 +356,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.88"/>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="26.25"/>
-    <col customWidth="1" min="4" max="4" width="17.75"/>
-    <col customWidth="1" min="5" max="5" width="6.5"/>
-    <col customWidth="1" min="7" max="7" width="6.0"/>
-    <col customWidth="1" min="8" max="8" width="43.63"/>
-    <col customWidth="1" min="9" max="9" width="15.75"/>
-    <col customWidth="1" min="10" max="10" width="26.88"/>
-    <col customWidth="1" min="11" max="11" width="33.75"/>
-    <col customWidth="1" min="12" max="12" width="23.5"/>
-    <col customWidth="1" min="13" max="13" width="13.38"/>
-    <col customWidth="1" min="14" max="14" width="35.25"/>
-    <col customWidth="1" min="15" max="15" width="28.0"/>
-    <col customWidth="1" min="16" max="16" width="33.63"/>
-    <col customWidth="1" min="17" max="17" width="18.13"/>
-    <col customWidth="1" min="18" max="18" width="32.38"/>
-    <col customWidth="1" min="19" max="19" width="14.63"/>
-    <col customWidth="1" min="22" max="22" width="53.5"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="19" width="22" customWidth="1"/>
+    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="22" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="64" customHeight="1">
+    <row r="1" ht="110" customHeight="1">
       <c r="A1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" ht="72" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>NO</t>

--- a/assets/report_templates/SPES_Report_Blank.xlsx
+++ b/assets/report_templates/SPES_Report_Blank.xlsx
@@ -68,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -86,6 +86,24 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1" vertical="center" horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1" vertical="center" horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1" vertical="center" horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -135,7 +153,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="11430000" cy="1298864"/>
+    <xdr:ext cx="13906500" cy="1580300"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="PESO Vinzons letterhead"/>
@@ -385,131 +403,131 @@
     <col min="27" max="27" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="110" customHeight="1">
+    <row r="1" ht="140" customHeight="1">
       <c r="A1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1"/>
     </row>
     <row r="3" ht="72" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>LAST NAME</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>FIRST NAME</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>MIDDLE NAME</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>SEX </t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>DATE OF BIRTH (yyyy/mm/dd)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>AGE</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>COMPLETE ADDRESS</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>BARANGAY</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>CONTACT NUMBER</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>SCHOOL</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>COURSE/STRAND</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>LEVEL</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>PARENT/GUARDIAN NAME</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="10" t="inlineStr">
         <is>
           <t>PARENT OCCUPATION</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="10" t="inlineStr">
         <is>
           <t>ESTIMATED MONTHLY INCOME</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>DATE OF APPLICATION
 (yyyy/mm/dd)</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>STATUS (PENDING/QUALIFIED/DISQUALIFIED)</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>WORK ASSIGNMENT</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>START DATE
 (yyyy/mm/dd)</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>END DATE
 (yyyy/mm/dd)</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
     </row>
     <row r="4" ht="42.75" customHeight="1">
       <c r="A4" s="4">

--- a/assets/report_templates/SPES_Report_Blank.xlsx
+++ b/assets/report_templates/SPES_Report_Blank.xlsx
@@ -148,10 +148,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>909638</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="13906500" cy="1580300"/>
     <xdr:pic>

--- a/assets/report_templates/SPES_Report_Blank.xlsx
+++ b/assets/report_templates/SPES_Report_Blank.xlsx
@@ -148,8 +148,8 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>909638</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
